--- a/business_surveys/050_influential_companies_survey--business_surveys.xlsx
+++ b/business_surveys/050_influential_companies_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'retail'}</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Retail'}</t>
+          <t>Retail</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'financial'}</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Financial'}</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Strong'}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_strong'}</t>
+          <t>somewhat_strong</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat strong'}</t>
+          <t>Somewhat strong</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'weak'}</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Weak'}</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very_weak'}</t>
+          <t>very_weak</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very weak'}</t>
+          <t>Very weak</t>
         </is>
       </c>
     </row>
